--- a/templates/_masters/OPS-005-supply-inventory-par-level-BLANK.xlsx
+++ b/templates/_masters/OPS-005-supply-inventory-par-level-BLANK.xlsx
@@ -542,7 +542,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="2">
     <dxf>
       <font>
         <b val="1"/>
@@ -550,18 +550,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFD6D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="00B91C1C"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFB3B3"/>
+          <fgColor rgb="00FFCCCC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5793,7 +5782,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6:F205">
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="2" dxfId="0">
       <formula>AND(ISNUMBER(F6),F6=0,ISNUMBER(E6),E6&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9750,7 +9739,7 @@
     <mergeCell ref="A4:L4"/>
   </mergeCells>
   <conditionalFormatting sqref="A8:I107">
-    <cfRule type="expression" priority="1" dxfId="2">
+    <cfRule type="expression" priority="1" dxfId="1">
       <formula>AND(ISNUMBER($G8),ISNUMBER($E8),$G8&gt;=$E8)</formula>
     </cfRule>
   </conditionalFormatting>
